--- a/output/pdf_financials_xlsx/CAPT.xlsx
+++ b/output/pdf_financials_xlsx/CAPT.xlsx
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.138656</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.138656</v>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
@@ -3328,13 +3328,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.380192</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.920719</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.72686</v>
       </c>
     </row>
     <row r="93">
@@ -5505,7 +5505,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -6036,7 +6040,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -6703,7 +6711,11 @@
           <t>Reserves 10 380,192</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -7466,7 +7478,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CAPT.xlsx
+++ b/output/pdf_financials_xlsx/CAPT.xlsx
@@ -741,13 +741,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.036561</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.020004</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.134141</v>
       </c>
     </row>
     <row r="13">
@@ -1205,13 +1205,13 @@
         <v>-0.66043</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.746411</v>
+        <v>-0.70985</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.313556</v>
+        <v>-1.293552</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.497712</v>
+        <v>-1.363571</v>
       </c>
     </row>
     <row r="28">
@@ -1261,13 +1261,13 @@
         <v>-0.66043</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.745312</v>
+        <v>-0.708751</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.312811</v>
+        <v>-1.292807</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.496861</v>
+        <v>-1.36272</v>
       </c>
     </row>
     <row r="30">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.40363</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.40363</v>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
@@ -1412,13 +1412,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.521614</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.568421</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>4.897245</v>
       </c>
     </row>
     <row r="35">
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.40363</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.40363</v>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.521614</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.568421</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>4.897245</v>
       </c>
     </row>
     <row r="37">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">

--- a/output/pdf_financials_xlsx/CAPT.xlsx
+++ b/output/pdf_financials_xlsx/CAPT.xlsx
@@ -607,7 +607,7 @@
         <v>0.434014</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.866303</v>
+        <v>0.894803</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +691,7 @@
         <v>0.434014</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.866303</v>
+        <v>0.894803</v>
       </c>
     </row>
     <row r="11">
@@ -719,7 +719,7 @@
         <v>-0.434014</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.866303</v>
+        <v>-0.894803</v>
       </c>
     </row>
     <row r="12">
@@ -1230,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.000511</v>
       </c>
       <c r="F28" s="3" t="n">
         <v>0.001099</v>
@@ -1258,7 +1258,7 @@
         <v>-0.918758</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.66043</v>
+        <v>-0.659919</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.708751</v>
@@ -1404,12 +1404,10 @@
         <v>2.40363</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>2.40363</v>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.710583</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0.07888199999999999</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.521614</v>
@@ -1438,10 +1436,8 @@
       <c r="D35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="3" t="n">
         <v>0</v>
@@ -1468,12 +1464,10 @@
         <v>2.40363</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.40363</v>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.710583</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0.07888199999999999</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.521614</v>
@@ -1502,10 +1496,8 @@
       <c r="D37" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
         <v>0</v>
@@ -1534,10 +1526,8 @@
       <c r="D38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="3" t="n">
         <v>0</v>
@@ -1566,10 +1556,8 @@
       <c r="D39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>0</v>
@@ -1598,10 +1586,8 @@
       <c r="D40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
         <v>0</v>
@@ -1630,10 +1616,8 @@
       <c r="D41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>0</v>
@@ -1662,10 +1646,8 @@
       <c r="D42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>0</v>
@@ -1694,10 +1676,8 @@
       <c r="D43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>0</v>
@@ -1726,10 +1706,8 @@
       <c r="D44" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>0</v>
@@ -1758,10 +1736,8 @@
       <c r="D45" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>0</v>
@@ -1790,10 +1766,8 @@
       <c r="D46" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>0</v>
@@ -1822,10 +1796,8 @@
       <c r="D47" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
         <v>0</v>
@@ -1854,10 +1826,8 @@
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -1928,10 +1898,8 @@
       <c r="D50" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="3" t="n">
         <v>0</v>
@@ -1960,10 +1928,8 @@
       <c r="D51" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="3" t="n">
         <v>0</v>
@@ -1992,10 +1958,8 @@
       <c r="D52" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="3" t="n">
         <v>0</v>
@@ -2024,10 +1988,8 @@
       <c r="D53" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E53" s="3" t="n">
+        <v>0.002246</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>0.001411</v>
@@ -2056,10 +2018,8 @@
       <c r="D54" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
         <v>0</v>
@@ -2130,10 +2090,8 @@
       <c r="D56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="3" t="n">
         <v>0</v>
@@ -2162,10 +2120,8 @@
       <c r="D57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
         <v>0</v>
@@ -2192,12 +2148,10 @@
         <v>3.573242</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3.573242</v>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.655126</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>7.832792</v>
       </c>
       <c r="F58" s="3" t="n">
         <v>10.260774</v>
@@ -2226,10 +2180,8 @@
       <c r="D59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
         <v>0</v>
@@ -2258,10 +2210,8 @@
       <c r="D60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="3" t="n">
         <v>0</v>
@@ -2290,10 +2240,8 @@
       <c r="D61" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
@@ -2362,12 +2310,10 @@
         <v>2.551362</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>2.551362</v>
-      </c>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.787712</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>0.150482</v>
       </c>
       <c r="F63" s="3" t="n">
         <v>0.613411</v>
@@ -2396,10 +2342,8 @@
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -2428,10 +2372,8 @@
       <c r="D65" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="3" t="n">
         <v>0</v>
@@ -2460,10 +2402,8 @@
       <c r="D66" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="3" t="n">
         <v>0</v>
@@ -2492,10 +2432,8 @@
       <c r="D67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -2522,12 +2460,10 @@
         <v>0.042076</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.042076</v>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.181733</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.264687</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>0.043391</v>
@@ -2556,10 +2492,8 @@
       <c r="D69" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>0</v>
@@ -2588,10 +2522,8 @@
       <c r="D70" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
@@ -2620,10 +2552,8 @@
       <c r="D71" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0</v>
@@ -2652,10 +2582,8 @@
       <c r="D72" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="3" t="n">
         <v>0</v>
@@ -2684,10 +2612,8 @@
       <c r="D73" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="3" t="n">
         <v>0</v>
@@ -2716,10 +2642,8 @@
       <c r="D74" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="3" t="n">
         <v>0</v>
@@ -2748,10 +2672,8 @@
       <c r="D75" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>0</v>
@@ -2822,10 +2744,8 @@
       <c r="D77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="3" t="n">
         <v>0</v>
@@ -2854,10 +2774,8 @@
       <c r="D78" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="3" t="n">
         <v>0</v>
@@ -2886,10 +2804,8 @@
       <c r="D79" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>0</v>
@@ -2960,10 +2876,8 @@
       <c r="D81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="3" t="n">
         <v>0</v>
@@ -2992,10 +2906,8 @@
       <c r="D82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="3" t="n">
         <v>0</v>
@@ -3024,10 +2936,8 @@
       <c r="D83" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="3" t="n">
         <v>0</v>
@@ -3056,10 +2966,8 @@
       <c r="D84" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="3" t="n">
         <v>0</v>
@@ -3088,10 +2996,8 @@
       <c r="D85" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="3" t="n">
         <v>0</v>
@@ -3160,12 +3066,10 @@
         <v>0.042076</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>0.042076</v>
-      </c>
-      <c r="E87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.200123</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>0.278088</v>
       </c>
       <c r="F87" s="3" t="n">
         <v>0.049869</v>
@@ -3192,12 +3096,10 @@
         <v>7.080929</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>7.080929</v>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.43879</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>10.43879</v>
       </c>
       <c r="F88" s="3" t="n">
         <v>13.827959</v>
@@ -3226,10 +3128,8 @@
       <c r="D89" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="3" t="n">
         <v>0</v>
@@ -3256,12 +3156,10 @@
         <v>-1.116479</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>-1.116479</v>
-      </c>
-      <c r="E90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.035237</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>-2.695667</v>
       </c>
       <c r="F90" s="3" t="n">
         <v>-3.442078</v>
@@ -3288,12 +3186,10 @@
         <v>-0.020578</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>-0.020578</v>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.109487</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0.199963</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>0.9319460000000001</v>
@@ -3320,12 +3216,10 @@
         <v>0.138656</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.138656</v>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.293727</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0.360023</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0.380192</v>
@@ -3354,10 +3248,8 @@
       <c r="D93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="3" t="n">
         <v>0</v>
@@ -3384,12 +3276,10 @@
         <v>6.082528</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>6.082528</v>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.587793</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>8.303108999999999</v>
       </c>
       <c r="F94" s="3" t="n">
         <v>11.698019</v>
@@ -3418,10 +3308,8 @@
       <c r="D95" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="3" t="n">
         <v>0</v>
@@ -3448,12 +3336,10 @@
         <v>6.082528</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>6.082528</v>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.587793</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>8.303108999999999</v>
       </c>
       <c r="F96" s="3" t="n">
         <v>11.698019</v>
@@ -3480,12 +3366,10 @@
         <v>2.384031744613269</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>2.384031744613269</v>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.080588310413701</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>55.17675868210151</v>
       </c>
       <c r="F97" s="3" t="n">
         <v>19.07044216683431</v>
@@ -3519,10 +3403,8 @@
       <c r="D99" s="3" t="n">
         <v>-0.918758</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="3" t="n">
+        <v>-0.66043</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-0.746411</v>
@@ -3549,10 +3431,8 @@
       <c r="D100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -3579,10 +3459,8 @@
       <c r="D101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
         <v>0</v>
@@ -3609,10 +3487,8 @@
       <c r="D102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="3" t="n">
         <v>0</v>
@@ -3639,10 +3515,8 @@
       <c r="D103" s="3" t="n">
         <v>-0.038062</v>
       </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="3" t="n">
+        <v>0.018951</v>
       </c>
       <c r="F103" s="3" t="n">
         <v>-0.034285</v>
@@ -3669,10 +3543,8 @@
       <c r="D104" s="3" t="n">
         <v>0.014337</v>
       </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" s="3" t="n">
+        <v>0.15427</v>
       </c>
       <c r="F104" s="3" t="n">
         <v>-0.181138</v>
@@ -3699,10 +3571,8 @@
       <c r="D105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="3" t="n">
         <v>0</v>
@@ -3727,12 +3597,10 @@
         <v>-1.067561</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-1.04288</v>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.131789</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.361757</v>
       </c>
       <c r="F106" s="3" t="n">
         <v>-1.181157</v>
@@ -3759,10 +3627,8 @@
       <c r="D107" s="3" t="n">
         <v>0.155071</v>
       </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="3" t="n">
+        <v>0.06629599999999999</v>
       </c>
       <c r="F107" s="3" t="n">
         <v>0.020169</v>
@@ -3789,10 +3655,8 @@
       <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -3819,10 +3683,8 @@
       <c r="D109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="3" t="n">
         <v>0</v>
@@ -3849,10 +3711,8 @@
       <c r="D110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -3879,19 +3739,17 @@
       <c r="D111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E111" s="3" t="n">
+        <v>-0.002572</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002572</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002326</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000958</v>
       </c>
     </row>
     <row r="112">
@@ -3909,10 +3767,8 @@
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -3939,10 +3795,8 @@
       <c r="D113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="3" t="n">
         <v>0</v>
@@ -3969,10 +3823,8 @@
       <c r="D114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
@@ -3999,10 +3851,8 @@
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -4029,10 +3879,8 @@
       <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>0</v>
@@ -4059,10 +3907,8 @@
       <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="3" t="n">
         <v>0</v>
@@ -4089,10 +3935,8 @@
       <c r="D118" s="3" t="n">
         <v>-1.938174</v>
       </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="3" t="n">
+        <v>-2.267372</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>-1.576111</v>
@@ -4119,10 +3963,8 @@
       <c r="D119" s="3" t="n">
         <v>-1.963174</v>
       </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E119" s="3" t="n">
+        <v>-2.269944</v>
       </c>
       <c r="F119" s="3" t="n">
         <v>-1.576111</v>
@@ -4149,10 +3991,8 @@
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -4179,10 +4019,8 @@
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -4209,10 +4047,8 @@
       <c r="D122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="3" t="n">
         <v>0</v>
@@ -4239,10 +4075,8 @@
       <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="3" t="n">
         <v>0</v>
@@ -4269,10 +4103,8 @@
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -4299,10 +4131,8 @@
       <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -4329,10 +4159,8 @@
       <c r="D126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="3" t="n">
         <v>0</v>
@@ -4401,10 +4229,8 @@
       <c r="D128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="3" t="n">
         <v>0</v>
@@ -4467,10 +4293,8 @@
       <c r="D130" s="3" t="n">
         <v>2.40363</v>
       </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E130" s="3" t="n">
+        <v>2.710583</v>
       </c>
       <c r="F130" s="3" t="n">
         <v>0.07888199999999999</v>
@@ -4497,10 +4321,8 @@
       <c r="D131" s="3" t="n">
         <v>-0.088909</v>
       </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="3" t="n">
         <v>0</v>
@@ -4527,10 +4349,8 @@
       <c r="D132" s="3" t="n">
         <v>0.306953</v>
       </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E132" s="3" t="n">
+        <v>-2.631701</v>
       </c>
       <c r="F132" s="3" t="n">
         <v>0.442732</v>
@@ -4559,10 +4379,8 @@
       <c r="D133" s="3" t="n">
         <v>2.710583</v>
       </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E133" s="3" t="n">
+        <v>0.07888199999999999</v>
       </c>
       <c r="F133" s="3" t="n">
         <v>0.521614</v>
@@ -4589,19 +4407,17 @@
       <c r="D134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="3" t="n">
+        <v>-0.002572</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002572</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002326</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000958</v>
       </c>
     </row>
     <row r="135">
@@ -4629,13 +4445,13 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.181157</v>
+        <v>-1.183729</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.833541</v>
+        <v>-0.835867</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-2.79538</v>
+        <v>-2.796338</v>
       </c>
     </row>
   </sheetData>
@@ -4649,7 +4465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K210"/>
+  <dimension ref="A1:K227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4741,12 +4557,10 @@
         <v>2.40363</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2.40363</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.710583</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>0.07888199999999999</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0.521614</v>
@@ -4785,15 +4599,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G3" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>0.025</v>
@@ -5031,12 +4841,10 @@
         <v>2.551362</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2.551362</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.787712</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.150482</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>0.613411</v>
@@ -5231,12 +5039,10 @@
         <v>6.124604</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>6.124604</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.787915999999999</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>8.581197</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>11.747888</v>
@@ -5314,15 +5120,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G14" s="5" t="n">
+        <v>0.01839</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.013401</v>
       </c>
       <c r="I14" s="5" t="n">
         <v>0.006478</v>
@@ -5364,12 +5166,10 @@
         <v>0.042076</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.042076</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.200123</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.278088</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>0.049869</v>
@@ -5572,12 +5372,10 @@
         <v>-0.020578</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.020578</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.109487</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.199963</v>
       </c>
       <c r="I19" s="5" t="n">
         <v>0.9319460000000001</v>
@@ -5619,12 +5417,10 @@
         <v>-1.116479</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-1.116479</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.035237</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-2.695667</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>-3.442078</v>
@@ -5666,12 +5462,10 @@
         <v>6.082528</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>6.082528</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.587793</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>8.303108999999999</v>
       </c>
       <c r="I21" s="5" t="n">
         <v>11.698019</v>
@@ -5713,12 +5507,10 @@
         <v>6.124604</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>6.124604</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.787915999999999</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>8.581197</v>
       </c>
       <c r="I22" s="5" t="n">
         <v>11.747888</v>
@@ -5757,15 +5549,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G23" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>2e-05</v>
       </c>
       <c r="I23" s="5" t="n">
         <v>0.002025</v>
@@ -5805,12 +5593,10 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.097022</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007412</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.020834</v>
       </c>
       <c r="I24" s="5" t="n">
         <v>0.006746</v>
@@ -5852,12 +5638,10 @@
         </is>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.006655</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.044717</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.025766</v>
       </c>
       <c r="I25" s="5" t="n">
         <v>0.060051</v>
@@ -5898,15 +5682,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" s="5" t="n">
+        <v>0.345078</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.595677</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>0.872292</v>
@@ -6966,13 +6746,21 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>assets</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Notes September</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Equipment 8</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -6983,13 +6771,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G47" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.002246</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -7013,30 +6801,34 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>assets</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Share subscriptions receivable 9</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Exploration and evaluation assets 9</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F48" s="5" t="n">
+        <v>3.573242</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.044055</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.655126</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>7.832792</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -7060,19 +6852,15 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Share capital 9 $</t>
+          <t>Accounts payable and accrued liabilities 11 $</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -7086,12 +6874,10 @@
         </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>7.080929</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.181733</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.264687</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -7122,10 +6908,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Subsequent events (Note</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Share capital 10</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -7137,12 +6927,10 @@
         </is>
       </c>
       <c r="G50" s="5" t="n">
-        <v>1.5e-05</v>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.43879</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>10.43879</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -7166,15 +6954,19 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Shareholders’ Equity</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Restricted cash 6</t>
+          <t>Reserves 10</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>RestrictedCash</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7182,18 +6974,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F51" s="5" t="n">
+        <v>0.138656</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.293727</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.360023</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -7220,7 +7008,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Share subscriptions receivable</t>
+          <t>Notes September</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -7229,13 +7017,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>0.044055</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -7267,24 +7055,22 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Taxes receivable 7</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TaxesReceivable</t>
-        </is>
-      </c>
+          <t>Share subscriptions receivable 9</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>0.097022</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.35249</v>
+        <v>0.044055</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -7313,15 +7099,19 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Shareholders’ Equity</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Prepaid expenses 8</t>
+          <t>Share capital 9 $</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PrepaidAssets</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7329,11 +7119,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
-        <v>0.006655</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.044717</v>
+        <v>7.080929</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -7364,29 +7156,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>assets</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets 9</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NetPPE</t>
-        </is>
-      </c>
+          <t>Subsequent events (Note</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>3.573242</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>5.655126</v>
+        <v>1.5e-05</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -7415,19 +7205,15 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Share capital 10 $</t>
+          <t>Restricted cash 6</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CapitalStock</t>
+          <t>RestrictedCash</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7435,11 +7221,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F56" s="5" t="n">
-        <v>7.080929</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>10.43879</v>
+        <v>0.025</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -7468,31 +7256,25 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Shareholders’ Equity</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Reserves 10</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
+          <t>Share subscriptions receivable</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.138656</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.293727</v>
+        <v>0.044055</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -7521,27 +7303,27 @@
           <t>balance_sheet</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Subsequent events</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>On behalf of the Board on December</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Taxes receivable 7</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TaxesReceivable</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.002021</v>
+        <v>0.097022</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>1.5e-05</v>
+        <v>0.35249</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -7567,22 +7349,18 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>OPERATING ACTIVITIES</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Prepaid expenses 8</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7590,50 +7368,52 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F59" s="5" t="n">
+        <v>0.006655</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.044717</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="5" t="n">
-        <v>-0.746411</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>-1.313556</v>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>-1.497712</v>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Share capital 10 $</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7641,80 +7421,80 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F60" s="5" t="n">
+        <v>7.080929</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>10.43879</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="5" t="n">
-        <v>0.001099</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>0.000745</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>0.000851</v>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Subsequent events</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>On behalf of the Board on December</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F61" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>1.5e-05</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="5" t="n">
-        <v>0.020169</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>0.540527</v>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>0.151828</v>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -7725,15 +7505,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -7744,24 +7528,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="5" t="n">
+        <v>-0.918758</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>-0.66043</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>0.10623</v>
+        <v>-0.746411</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>-0.283194</v>
+        <v>-1.313556</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0.119065</v>
+        <v>-1.497712</v>
       </c>
     </row>
     <row r="63">
@@ -7772,41 +7552,45 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0.042076</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.042076</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.014337</v>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0.000511</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>-0.181138</v>
+        <v>0.001099</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>3.6e-05</v>
+        <v>0.000745</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>0.126751</v>
+        <v>0.000851</v>
       </c>
     </row>
     <row r="64">
@@ -7817,15 +7601,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VAT receivable</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -7836,26 +7624,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G64" s="5" t="n">
+        <v>0.155071</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0.06629599999999999</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>0.020169</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>0.222876</v>
+        <v>0.540527</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-1.431203</v>
+        <v>0.151828</v>
       </c>
     </row>
     <row r="65">
@@ -7866,19 +7648,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -7889,28 +7667,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G65" s="5" t="n">
+        <v>-0.088909</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.341524</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.10623</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>-0.283194</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.170711</v>
+        <v>0.119065</v>
       </c>
     </row>
     <row r="66">
@@ -7926,36 +7696,34 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>-0.006655</v>
+        <v>0.042076</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.006655</v>
+        <v>0.042076</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-0.038062</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014337</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0.15427</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>-0.034285</v>
+        <v>-0.181138</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>-0.000975</v>
+        <v>3.6e-05</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.094249</v>
+        <v>0.126751</v>
       </c>
     </row>
     <row r="67">
@@ -7971,36 +7739,40 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items total</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>-1.067561</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>-1.067561</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>-1.04288</v>
+          <t>VAT receivable</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="5" t="n">
-        <v>-1.181157</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-0.833541</v>
+        <v>0.222876</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-2.79538</v>
+        <v>-1.431203</v>
       </c>
     </row>
     <row r="68">
@@ -8011,17 +7783,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -8044,14 +7816,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="5" t="n">
-        <v>-1.576111</v>
-      </c>
-      <c r="J68" s="5" t="n">
-        <v>-1.137326</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-5.294954</v>
+        <v>-0.170711</v>
       </c>
     </row>
     <row r="69">
@@ -8062,45 +7838,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Acquisition of equipment</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>-0.006655</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-0.006655</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>-0.038062</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0.018951</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>-0.034285</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>-0.002326</v>
+        <v>-0.000975</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.000958</v>
+        <v>-0.094249</v>
       </c>
     </row>
     <row r="70">
@@ -8111,41 +7881,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES total</t>
+          <t>Changes in non-cash working capital items total</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>-0.073242</v>
+        <v>-1.067561</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.073242</v>
+        <v>-1.067561</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-1.963174</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.131789</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>-0.361757</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>-1.576111</v>
+        <v>-1.181157</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>-1.139652</v>
+        <v>-0.833541</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-5.295912</v>
+        <v>-2.79538</v>
       </c>
     </row>
     <row r="71">
@@ -8156,15 +7924,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance costs</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -8175,24 +7947,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G71" s="5" t="n">
+        <v>-1.938174</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>-2.267372</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>3.2</v>
+        <v>-1.576111</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>2.02</v>
+        <v>-1.137326</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>5.3</v>
+        <v>-5.294954</v>
       </c>
     </row>
     <row r="72">
@@ -8203,15 +7971,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Net proceeds from warrants exercised</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Acquisition of equipment</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -8227,23 +7999,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H72" s="5" t="n">
+        <v>-0.002572</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J72" s="5" t="n">
+        <v>-0.002326</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>6.625</v>
+        <v>-0.000958</v>
       </c>
     </row>
     <row r="73">
@@ -8254,47 +8022,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Net proceeds from options exercised</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>INVESTING ACTIVITIES total</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>-0.073242</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>-0.073242</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>-1.963174</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>-2.269944</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>-1.576111</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-1.139652</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0.495116</v>
+        <v>-5.295912</v>
       </c>
     </row>
     <row r="74">
@@ -8310,16 +8070,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES total</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>3.565011</v>
+          <t>Proceeds from shares issuance, net of issuance costs</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8343,7 +8101,7 @@
         <v>2.02</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>12.420116</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="75">
@@ -8359,16 +8117,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>2.40363</v>
+          <t>Net proceeds from warrants exercised</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8385,14 +8141,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="5" t="n">
-        <v>0.442732</v>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>0.046807</v>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K75" s="5" t="n">
-        <v>4.328824</v>
+        <v>6.625</v>
       </c>
     </row>
     <row r="76">
@@ -8408,14 +8168,10 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Net proceeds from options exercised</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -8436,14 +8192,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="5" t="n">
-        <v>0.07888199999999999</v>
-      </c>
-      <c r="J76" s="5" t="n">
-        <v>0.521614</v>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K76" s="5" t="n">
-        <v>0.568421</v>
+        <v>0.495116</v>
       </c>
     </row>
     <row r="77">
@@ -8459,18 +8219,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cash, end of the year $</t>
+          <t>FINANCING ACTIVITIES total</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>3.565011</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8488,13 +8246,13 @@
         </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0.521614</v>
+        <v>3.2</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0.568421</v>
+        <v>2.02</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>4.897245</v>
+        <v>12.420116</v>
       </c>
     </row>
     <row r="78">
@@ -8505,19 +8263,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Non-Cash Investing and Financing Activities</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Share subscription receivable</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase in cash</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>2.40363</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8534,18 +8294,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I78" s="5" t="n">
+        <v>0.442732</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>0.046807</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>0.043</v>
+        <v>4.328824</v>
       </c>
     </row>
     <row r="79">
@@ -8556,15 +8312,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Non-Cash Investing and Financing Activities</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Shares issued for royalty acquisition</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -8585,18 +8345,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="5" t="n">
+        <v>0.07888199999999999</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>0.521614</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>0.552791</v>
+        <v>0.568421</v>
       </c>
     </row>
     <row r="80">
@@ -8607,17 +8363,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Non-Cash Investing and Financing Activities</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Accounts payable included in exploration and evaluation assets</t>
+          <t>Cash, end of the year $</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8640,16 +8396,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="5" t="n">
+        <v>0.521614</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>0.004477</v>
+        <v>0.568421</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>0.138358</v>
+        <v>4.897245</v>
       </c>
     </row>
     <row r="81">
@@ -8665,7 +8419,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Equity reserve transferred to share capital on exercise of stock options</t>
+          <t>Share subscription receivable</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -8700,7 +8454,7 @@
         </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>0.345687</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="82">
@@ -8711,12 +8465,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Note          Shares         Amount             Reserves        (Income)/Loss                 Deficit                Total</t>
+          <t>Non-Cash Investing and Financing Activities</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Balance at September 30, 2023 70,590,771 $ 13,827,959 $ 380,192 $ 931,946 $</t>
+          <t>Shares issued for royalty acquisition</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -8740,14 +8494,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="5" t="n">
-        <v>11.698019</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>11.698019</v>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-3.442078</v>
+        <v>0.552791</v>
       </c>
     </row>
     <row r="83">
@@ -8758,15 +8516,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Note          Shares         Amount             Reserves        (Income)/Loss                 Deficit                Total</t>
+          <t>Non-Cash Investing and Financing Activities</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Private placement 8 13,466,667 2,020,000 - -</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Accounts payable included in exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -8793,12 +8555,10 @@
         </is>
       </c>
       <c r="J83" s="5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004477</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0.138358</v>
       </c>
     </row>
     <row r="84">
@@ -8809,12 +8569,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Note          Shares         Amount             Reserves        (Income)/Loss                 Deficit                Total</t>
+          <t>Non-Cash Investing and Financing Activities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Share-based compensation 8 - - 540,527 -</t>
+          <t>Equity reserve transferred to share capital on exercise of stock options</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -8843,13 +8603,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J84" s="5" t="n">
-        <v>0.540527</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0.345687</v>
       </c>
     </row>
     <row r="85">
@@ -8865,7 +8625,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Foreign exchange movement - - - (1,043,049)</t>
+          <t>Balance at September 30, 2023 70,590,771 $ 13,827,959 $ 380,192 $ 931,946 $</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -8890,15 +8650,13 @@
         </is>
       </c>
       <c r="I85" s="5" t="n">
-        <v>-1.043049</v>
+        <v>11.698019</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>-1.043049</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.698019</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>-3.442078</v>
       </c>
     </row>
     <row r="86">
@@ -8914,14 +8672,10 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Private placement 8 13,466,667 2,020,000 - -</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -8942,14 +8696,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="5" t="n">
-        <v>-0.746411</v>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-1.313556</v>
-      </c>
-      <c r="K86" s="5" t="n">
-        <v>-1.313556</v>
+        <v>2.02</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -8965,7 +8723,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Balance at September 30, 2024 84,057,438 $ 15,847,959 $ 920,719 $ (111,103) $</t>
+          <t>Share-based compensation 8 - - 540,527 -</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -8989,14 +8747,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n">
-        <v>11.901941</v>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J87" s="5" t="n">
-        <v>11.901941</v>
-      </c>
-      <c r="K87" s="5" t="n">
-        <v>-4.755634</v>
+        <v>0.540527</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -9012,7 +8774,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Private placement 8 13,250,000 5,300,000 - -</t>
+          <t>Foreign exchange movement - - - (1,043,049)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -9036,13 +8798,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I88" s="5" t="n">
+        <v>-1.043049</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>5.3</v>
+        <v>-1.043049</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -9063,10 +8823,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Shares issued for royalty acquisition 7, 8 1,422,002 552,791 - -</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -9087,18 +8851,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="5" t="n">
+        <v>-0.746411</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>0.552791</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.313556</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-1.313556</v>
       </c>
     </row>
     <row r="90">
@@ -9114,7 +8874,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Shares issued for warrants exercised 8 13,250,000 6,625,000 - -</t>
+          <t>Balance at September 30, 2024 84,057,438 $ 15,847,959 $ 920,719 $ (111,103) $</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -9138,18 +8898,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" s="5" t="n">
+        <v>11.901941</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>6.625</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.901941</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-4.755634</v>
       </c>
     </row>
     <row r="91">
@@ -9165,7 +8921,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Shares issued for options exercised 8 2,256,166 883,803 (345,687) -</t>
+          <t>Private placement 8 13,250,000 5,300,000 - -</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -9195,7 +8951,7 @@
         </is>
       </c>
       <c r="J91" s="5" t="n">
-        <v>0.538116</v>
+        <v>5.3</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -9216,7 +8972,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Share-based compensation 8 - - 151,828 -</t>
+          <t>Shares issued for royalty acquisition 7, 8 1,422,002 552,791 - -</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -9246,7 +9002,7 @@
         </is>
       </c>
       <c r="J92" s="5" t="n">
-        <v>0.151828</v>
+        <v>0.552791</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -9267,7 +9023,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Foreign exchange movement - - - 992,096</t>
+          <t>Shares issued for warrants exercised 8 13,250,000 6,625,000 - -</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -9297,7 +9053,7 @@
         </is>
       </c>
       <c r="J93" s="5" t="n">
-        <v>0.992096</v>
+        <v>6.625</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -9318,7 +9074,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Balance at September 30, 2025 114,235,606 $ 29,209,553 $ 726,860 $ 880,993 $</t>
+          <t>Shares issued for options exercised 8 2,256,166 883,803 (345,687) -</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -9348,10 +9104,12 @@
         </is>
       </c>
       <c r="J94" s="5" t="n">
-        <v>24.56406</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>-6.253346</v>
+        <v>0.538116</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -9362,34 +9120,42 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Note          Shares         Amount             Reserves        (Income)/Loss                 Deficit                Total</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Taxes receivable</t>
+          <t>Share-based compensation 8 - - 151,828 -</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
-        <v>-0.097022</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>-0.097022</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>-0.255468</v>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="5" t="n">
-        <v>-0.346821</v>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="5" t="n">
-        <v>0.222876</v>
+        <v>0.151828</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -9410,7 +9176,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Balance at September 30, 2022 53,785,797 $ 10,438,790 $ 360,023 $ 199,963 $</t>
+          <t>Foreign exchange movement - - - 992,096</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -9434,11 +9200,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="5" t="n">
-        <v>8.303108999999999</v>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="5" t="n">
-        <v>-2.695667</v>
+        <v>0.992096</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -9459,7 +9227,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Private placement 9 16,000,000 3,200,000 - -</t>
+          <t>Balance at September 30, 2025 114,235,606 $ 29,209,553 $ 726,860 $ 880,993 $</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -9483,18 +9251,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>24.56406</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>-6.253346</v>
       </c>
     </row>
     <row r="98">
@@ -9505,42 +9271,32 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Note          Shares         Amount             Reserves        (Income)/Loss                 Deficit                Total</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Shares issued for property acquisition 8 804,974 189,169 - -</t>
+          <t>Taxes receivable</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E98" s="5" t="n">
+        <v>-0.097022</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>-0.097022</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>-0.255468</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>-0.282879</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.189169</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.346821</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>0.222876</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -9561,7 +9317,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Share-based payments 9 - - 20,169 -</t>
+          <t>Balance at September 30, 2022 53,785,797 $ 10,438,790 $ 360,023 $ 199,963 $</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -9586,12 +9342,10 @@
         </is>
       </c>
       <c r="I99" s="5" t="n">
-        <v>0.020169</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.303108999999999</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>-2.695667</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -9612,7 +9366,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Foreign exchange movement - - - 731,983</t>
+          <t>Private placement 9 16,000,000 3,200,000 - -</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -9637,7 +9391,7 @@
         </is>
       </c>
       <c r="I100" s="5" t="n">
-        <v>0.7319830000000001</v>
+        <v>3.2</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -9663,7 +9417,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Private placement 9 13,466,667 2,020,000 - -</t>
+          <t>Shares issued for property acquisition 8 804,974 189,169 - -</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -9688,7 +9442,7 @@
         </is>
       </c>
       <c r="I101" s="5" t="n">
-        <v>2.02</v>
+        <v>0.189169</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -9714,7 +9468,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Share-based payments 9 - - 540,527 -</t>
+          <t>Share-based payments 9 - - 20,169 -</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -9739,7 +9493,7 @@
         </is>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0.540527</v>
+        <v>0.020169</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -9765,7 +9519,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>For the Year ended September</t>
+          <t>Foreign exchange movement - - - 731,983</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -9790,10 +9544,12 @@
         </is>
       </c>
       <c r="I103" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="J103" s="5" t="n">
-        <v>3e-05</v>
+        <v>0.7319830000000001</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -9807,10 +9563,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Note          Shares         Amount             Reserves        (Income)/Loss                 Deficit                Total</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>For the Years ended September</t>
+          <t>Private placement 9 13,466,667 2,020,000 - -</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -9835,7 +9595,7 @@
         </is>
       </c>
       <c r="I104" s="5" t="n">
-        <v>3e-05</v>
+        <v>2.02</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -9856,12 +9616,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Note          Shares         Amount             Reserves        (Income)/Loss                 Deficit                Total</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Net loss for the year $ (746,411) $</t>
+          <t>Share-based payments 9 - - 540,527 -</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -9886,7 +9646,7 @@
         </is>
       </c>
       <c r="I105" s="5" t="n">
-        <v>-0.66043</v>
+        <v>0.540527</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -9907,19 +9667,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>Note          Shares         Amount             Reserves        (Income)/Loss                 Deficit                Total</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Depreciation 1,099</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>For the Year ended September</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -9941,12 +9697,10 @@
         </is>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.000511</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002024</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -9960,21 +9714,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Items not involving cash</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Share-based compensation 20,169</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>For the Years ended September</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -9996,7 +9742,7 @@
         </is>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0.06629599999999999</v>
+        <v>3e-05</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -10017,12 +9763,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Foreign exchange 106,230</t>
+          <t>Net loss for the year $ (746,411) $</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -10047,7 +9793,7 @@
         </is>
       </c>
       <c r="I108" s="5" t="n">
-        <v>-0.060567</v>
+        <v>-0.66043</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -10068,17 +9814,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (181,138)</t>
+          <t>Depreciation 1,099</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -10102,7 +9848,7 @@
         </is>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0.15427</v>
+        <v>0.000511</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -10123,15 +9869,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Taxes receivable (346,821)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Share-based compensation 20,169</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -10153,7 +9903,7 @@
         </is>
       </c>
       <c r="I110" s="5" t="n">
-        <v>-0.282879</v>
+        <v>0.06629599999999999</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -10174,12 +9924,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Prepaid expenses (34,285)</t>
+          <t>Foreign exchange 106,230</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -10204,7 +9954,7 @@
         </is>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0.018951</v>
+        <v>-0.060567</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -10225,15 +9975,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets (1,576,111)</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (181,138)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -10255,7 +10009,7 @@
         </is>
       </c>
       <c r="I112" s="5" t="n">
-        <v>-1.89754</v>
+        <v>0.15427</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -10276,12 +10030,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Acquisition of equipment -</t>
+          <t>Taxes receivable (346,821)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -10306,7 +10060,7 @@
         </is>
       </c>
       <c r="I113" s="5" t="n">
-        <v>-0.002572</v>
+        <v>-0.282879</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -10327,12 +10081,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance costs 3,200,000</t>
+          <t>Prepaid expenses (34,285)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -10356,10 +10110,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="5" t="n">
+        <v>0.018951</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -10380,12 +10132,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Share subscription receivable</t>
+          <t>Exploration and evaluation assets (1,576,111)</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -10409,10 +10161,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="5" t="n">
+        <v>-1.89754</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -10433,17 +10183,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash 442,732</t>
+          <t>Acquisition of equipment -</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10467,7 +10217,7 @@
         </is>
       </c>
       <c r="I116" s="5" t="n">
-        <v>-2.631701</v>
+        <v>-0.002572</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -10493,14 +10243,10 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year 78,882</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Proceeds from shares issuance, net of issuance costs 3,200,000</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -10521,8 +10267,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="5" t="n">
-        <v>2.710583</v>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -10548,14 +10296,10 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Cash, end of the year $ 521,614 $</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Share subscription receivable</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -10576,8 +10320,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="5" t="n">
-        <v>0.07888199999999999</v>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -10598,15 +10344,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>payable was $6,923 (September 30, 2022 - $54,004).</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Total 8,587,793 66,296 309,450 (660,430) 8,303,109 3,200,000 189,169 20,169 731,983 (746,411)</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Increase (decrease) in cash 442,732</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -10628,7 +10378,7 @@
         </is>
       </c>
       <c r="I119" s="5" t="n">
-        <v>11.698019</v>
+        <v>-2.631701</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -10649,15 +10399,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>payable was $6,923 (September 30, 2022 - $54,004).</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Deficit (2,035,237) - - (660,430) (2,695,667) - - - - (746,411)</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Cash, beginning of the year 78,882</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -10679,7 +10433,7 @@
         </is>
       </c>
       <c r="I120" s="5" t="n">
-        <v>-3.442078</v>
+        <v>2.710583</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -10700,15 +10454,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>$    $        $                                                                                                                                                                financial</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>$ $ $ these</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>Cash, end of the year $ 521,614 $</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -10730,7 +10488,7 @@
         </is>
       </c>
       <c r="I121" s="5" t="n">
-        <v>2.3e-05</v>
+        <v>0.07888199999999999</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -10751,12 +10509,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>of      of</t>
+          <t>payable was $6,923 (September 30, 2022 - $54,004).</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>- - - - - - part</t>
+          <t>Total 8,587,793 66,296 309,450 (660,430) 8,303,109 3,200,000 189,169 20,169 731,983 (746,411)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -10781,7 +10539,7 @@
         </is>
       </c>
       <c r="I122" s="5" t="n">
-        <v>9e-06</v>
+        <v>11.698019</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -10802,12 +10560,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>payable was $6,923 (September 30, 2022 - $54,004).</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>Deficit (2,035,237) - - (660,430) (2,695,667) - - - - (746,411)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -10831,10 +10589,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="5" t="n">
+        <v>-3.442078</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -10855,12 +10611,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>are</t>
+          <t>$    $        $                                                                                                                                                                financial</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Share notes Shares 53,785,797 53,785,797 16,000,000 804,974</t>
+          <t>$ $ $ these</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -10885,7 +10641,7 @@
         </is>
       </c>
       <c r="I124" s="5" t="n">
-        <v>70.590771</v>
+        <v>2.3e-05</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -10906,17 +10662,19 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Incorporation on</t>
+          <t>of      of</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Notes September 30,</t>
+          <t>- - - - - - part</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" s="5" t="n">
-        <v>0.00202</v>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10933,10 +10691,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="5" t="n">
+        <v>9e-06</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -10957,27 +10713,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>are</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="n">
-        <v>-1.116479</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>-1.116479</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>-0.918758</v>
+          <t>are</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -11008,21 +10766,19 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>are</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Share-based payments 9</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="n">
-        <v>0.110519</v>
+          <t>Share notes Shares 53,785,797 53,785,797 16,000,000 804,974</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11039,10 +10795,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="5" t="n">
+        <v>70.590771</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -11068,26 +10822,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets 8</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="n">
-        <v>-0.073242</v>
+          <t>Restricted cash</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="5" t="n">
+        <v>-0.025</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -11123,22 +10873,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance costs 9</t>
+          <t>Net proceeds from exercise of options</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
-      <c r="E129" s="5" t="n">
-        <v>3.565011</v>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="5" t="n">
+        <v>0.046086</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -11174,26 +10924,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>EffectOfExchangeRateChanges</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="n">
-        <v>-0.020578</v>
+          <t>Net proceeds from exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="5" t="n">
+        <v>0.111775</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -11224,12 +10970,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Proceeds from shares issuance, net of issuance</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cash, date of Incorporation</t>
+          <t>Proceeds from shares issuance, net of issuance costs</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -11243,10 +10989,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="5" t="n">
+        <v>3.2</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -11277,27 +11021,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Share subscription receivable                                                             44,055</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cash, September 30, 2020 $</t>
+          <t>Share subscription receivable                                                             44,055 total</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
-      <c r="E132" s="5" t="n">
-        <v>2.40363</v>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G132" s="5" t="n">
+        <v>3.401916</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -11328,32 +11072,34 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Note     Shares      Amount             Reserves                  Loss          Deficit          Total</t>
+          <t>Share subscription receivable                                                             44,055</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Balance at Incorporation 1 $ 1 $ - $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" s="5" t="n">
-        <v>1e-06</v>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G133" s="5" t="n">
+        <v>0.306953</v>
+      </c>
+      <c r="H133" s="5" t="n">
+        <v>-2.631701</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -11379,15 +11125,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Note     Shares      Amount             Reserves                  Loss          Deficit          Total</t>
+          <t>Share subscription receivable                                                             44,055</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Adjustment for fractional shares (89) - - - -</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -11398,15 +11148,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G134" s="5" t="n">
+        <v>2.40363</v>
+      </c>
+      <c r="H134" s="5" t="n">
+        <v>2.710583</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -11432,32 +11178,34 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Note     Shares      Amount             Reserves                  Loss          Deficit          Total</t>
+          <t>Share subscription receivable                                                             44,055</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Shares issued for mineral property 8 17,500,000 3,500,000 - - -</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" s="5" t="n">
-        <v>3.5</v>
+          <t>Cash, end of the year $</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="5" t="n">
+        <v>2.710583</v>
+      </c>
+      <c r="H135" s="5" t="n">
+        <v>0.07888199999999999</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -11483,32 +11231,30 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Note     Shares      Amount             Reserves                  Loss          Deficit          Total</t>
+          <t>payable was $54,004 (September 30, 2021 - $143,710).</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Private placement 9 19,204,425 3,550,873 28,137 - -</t>
+          <t>Total 6,082,528 111,775 46,086 3,200,000 155,071 (88,909) (918,758) 8,587,793 66,296 309,450</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
-      <c r="E136" s="5" t="n">
-        <v>3.57901</v>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G136" s="5" t="n">
+        <v>8.303108999999999</v>
+      </c>
+      <c r="H136" s="5" t="n">
+        <v>-0.66043</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -11534,32 +11280,30 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>payable was $54,004 (September 30, 2021 - $143,710).</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants exercised under Plan of Arrangement 9 155,923 30,055 - - -</t>
+          <t>Deficit (1,116,479) - - - - - (918,758) (2,035,237) - -</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
-      <c r="E137" s="5" t="n">
-        <v>0.030055</v>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G137" s="5" t="n">
+        <v>-2.695667</v>
+      </c>
+      <c r="H137" s="5" t="n">
+        <v>-0.66043</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -11585,27 +11329,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>payable was $54,004 (September 30, 2021 - $143,710).</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Share-based payments 9 - - 110,519 - -</t>
+          <t>Accumulated Other Comprehensive Loss (20,578) - - - - (88,909) - (109,487) - 309,450</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" s="5" t="n">
-        <v>0.110519</v>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G138" s="5" t="n">
+        <v>0.199963</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -11636,17 +11380,19 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>$                $                                                                                                                                                                             statements.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Foreign exchange movement - - - (20,578) -</t>
+          <t>$                $                                                                                                                                                                             statements.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" s="5" t="n">
-        <v>-0.020578</v>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11687,32 +11433,30 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>$                $                                                                                                                                                                             statements.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Loss for the period - - - - (1,116,479)</t>
+          <t>financial Reserves 138,656 155,071 293,727</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
-      <c r="E140" s="5" t="n">
-        <v>-1.116479</v>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G140" s="5" t="n">
+        <v>0.360023</v>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>0.06629599999999999</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -11738,32 +11482,30 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>of                                                                                                                                           Riverside’s                                 movement                                          movement                                                       Plan</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Balance at September 30, 2020 36,860,260 $ 7,080,929 $ 141,024 $ (20,578) $ (1,116,479) $</t>
+          <t>For the Year Ended September</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" s="5" t="n">
-        <v>6.082528</v>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G141" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="H141" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -11789,25 +11531,27 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Year             Incorporation on</t>
+          <t>Incorporation on</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ended October</t>
+          <t>Notes September 30,</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>0.002019</v>
-      </c>
-      <c r="G142" s="5" t="n">
-        <v>3e-05</v>
+      <c r="E142" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -11838,25 +11582,27 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Year             Incorporation on</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Notes 2021 September</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="n">
+        <v>-1.116479</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>0.00202</v>
+        <v>-1.116479</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>3e-05</v>
+        <v>-0.918758</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -11892,7 +11638,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Share-based payments 10</t>
+          <t>Share-based payments 9</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11900,16 +11646,18 @@
           <t>StockBasedCompensation</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="n">
+      <c r="E144" s="5" t="n">
         <v>0.110519</v>
       </c>
-      <c r="G144" s="5" t="n">
-        <v>0.155071</v>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -11945,7 +11693,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets 9</t>
+          <t>Exploration and evaluation assets 8</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -11953,16 +11701,18 @@
           <t>NetOtherInvestingChanges</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F145" s="5" t="n">
+      <c r="E145" s="5" t="n">
         <v>-0.073242</v>
       </c>
-      <c r="G145" s="5" t="n">
-        <v>-1.938174</v>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -11993,27 +11743,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Restricted cash 6</t>
+          <t>Proceeds from shares issuance, net of issuance costs 9</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E146" s="5" t="n">
+        <v>3.565011</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G146" s="5" t="n">
-        <v>-0.025</v>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -12049,22 +11799,26 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Net proceeds from exercise of options 10</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Effect of foreign exchange on cash</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="n">
+        <v>-0.020578</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G147" s="5" t="n">
-        <v>0.046086</v>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -12100,7 +11854,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Net proceeds from exercise of warrants 10</t>
+          <t>Cash, date of Incorporation</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -12114,8 +11868,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G148" s="5" t="n">
-        <v>0.111775</v>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -12146,25 +11902,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance costs 10</t>
+          <t>Cash, September 30, 2020 $</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F149" s="5" t="n">
-        <v>3.565011</v>
-      </c>
-      <c r="G149" s="5" t="n">
-        <v>3.2</v>
+      <c r="E149" s="5" t="n">
+        <v>2.40363</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -12195,27 +11953,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance</t>
+          <t>Note     Shares      Amount             Reserves                  Loss          Deficit          Total</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Share subscription receivable</t>
+          <t>Balance at Incorporation 1 $ 1 $ - $ - $ - $</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E150" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G150" s="5" t="n">
-        <v>0.044055</v>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -12246,12 +12004,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance</t>
+          <t>Note     Shares      Amount             Reserves                  Loss          Deficit          Total</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance total</t>
+          <t>Adjustment for fractional shares (89) - - - -</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -12260,11 +12018,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F151" s="5" t="n">
-        <v>3.565011</v>
-      </c>
-      <c r="G151" s="5" t="n">
-        <v>3.401916</v>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -12295,29 +12057,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance</t>
+          <t>Note     Shares      Amount             Reserves                  Loss          Deficit          Total</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Effect of foreign exchange on cash</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>EffectOfExchangeRateChanges</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F152" s="5" t="n">
-        <v>-0.020578</v>
-      </c>
-      <c r="G152" s="5" t="n">
-        <v>-0.088909</v>
+          <t>Shares issued for mineral property 8 17,500,000 3,500,000 - - -</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -12348,29 +12108,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance</t>
+          <t>Note     Shares      Amount             Reserves                  Loss          Deficit          Total</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F153" s="5" t="n">
-        <v>2.40363</v>
-      </c>
-      <c r="G153" s="5" t="n">
-        <v>0.306953</v>
+          <t>Private placement 9 19,204,425 3,550,873 28,137 - -</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" s="5" t="n">
+        <v>3.57901</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -12401,31 +12159,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Cash, beginning of the period</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares issued, re: Riverside’s warrants exercised under Plan of Arrangement 9 155,923 30,055 - - -</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" s="5" t="n">
+        <v>0.030055</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G154" s="5" t="n">
-        <v>2.40363</v>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -12456,29 +12210,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Proceeds from shares issuance, net of issuance</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Cash, end of the period $</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F155" s="5" t="n">
-        <v>2.40363</v>
-      </c>
-      <c r="G155" s="5" t="n">
-        <v>2.710583</v>
+          <t>Share-based payments 9 - - 110,519 - -</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" s="5" t="n">
+        <v>0.110519</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -12509,22 +12261,22 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Note      Shares       Amount       Reserves              e Loss               Deficit              Total</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Balance at Incorporation 1 $ 1 $ - $ - $</t>
+          <t>Foreign exchange movement - - - (20,578) -</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" s="5" t="n">
-        <v>1e-06</v>
+      <c r="E156" s="5" t="n">
+        <v>-0.020578</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -12560,19 +12312,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Note      Shares       Amount       Reserves              e Loss               Deficit              Total</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Adjustment for fractional shares (89) - - -</t>
+          <t>Loss for the period - - - - (1,116,479)</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E157" s="5" t="n">
+        <v>-1.116479</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -12613,22 +12363,22 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Note      Shares       Amount       Reserves              e Loss               Deficit              Total</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Shares issued for mineral property 9 17,500,000 3,500,000 - -</t>
+          <t>Balance at September 30, 2020 36,860,260 $ 7,080,929 $ 141,024 $ (20,578) $ (1,116,479) $</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>3.5</v>
+      <c r="E158" s="5" t="n">
+        <v>6.082528</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -12664,12 +12414,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Note      Shares       Amount       Reserves              e Loss               Deficit              Total</t>
+          <t>Year             Incorporation on</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Private placement 10 19,204,425 3,550,873 28,137 -</t>
+          <t>Ended October</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -12679,12 +12429,10 @@
         </is>
       </c>
       <c r="F159" s="5" t="n">
-        <v>3.57901</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002019</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -12715,12 +12463,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Share issued, re: Riverside’s warrants</t>
+          <t>Year             Incorporation on</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Share issued, re: Riverside’s warrants exercised under Plan of Arrangement 10 155,923 30,055 - -</t>
+          <t>Notes 2021 September</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -12730,12 +12478,10 @@
         </is>
       </c>
       <c r="F160" s="5" t="n">
-        <v>0.030055</v>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00202</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -12766,15 +12512,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Share issued, re: Riverside’s warrants</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Share-based payments 10 - - 110,519 -</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Share-based payments 10</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -12783,10 +12533,8 @@
       <c r="F161" s="5" t="n">
         <v>0.110519</v>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G161" s="5" t="n">
+        <v>0.155071</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -12817,27 +12565,29 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Share issued, re: Riverside’s warrants</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Foreign exchange movement - - - (20,578)</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Exploration and evaluation assets 9</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F162" s="5" t="n">
-        <v>-0.020578</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.073242</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>-1.938174</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -12868,12 +12618,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>on October 30, 2019 to September 30,</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>on October 30, 2019 to September 30,</t>
+          <t>Restricted cash 6</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12882,11 +12632,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F163" s="5" t="n">
-        <v>-1.116479</v>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>-1.116479</v>
+        <v>-0.025</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -12917,12 +12669,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>on October 30, 2019 to September 30,</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Balance at September 30, 2020 36,860,260 7,080,929 138,656 (20,578)</t>
+          <t>Net proceeds from exercise of options 10</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -12931,11 +12683,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F164" s="5" t="n">
-        <v>6.082528</v>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>-1.116479</v>
+        <v>0.046086</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -12966,12 +12720,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>on October 30, 2019 to September 30,</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Exercise of options 10 345,651 46,086 - -</t>
+          <t>Net proceeds from exercise of warrants 10</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12980,13 +12734,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F165" s="5" t="n">
-        <v>0.046086</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.111775</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -13017,12 +12771,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>Proceeds from shares issuance, net of issuance</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants exercised under Plan of Arrangement 10 579,886 111,775 - -</t>
+          <t>Proceeds from shares issuance, net of issuance costs 10</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -13032,12 +12786,10 @@
         </is>
       </c>
       <c r="F166" s="5" t="n">
-        <v>0.111775</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.565011</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>3.2</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -13068,12 +12820,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>Proceeds from shares issuance, net of issuance</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Private placement 10 16,000,000 3,200,000 - -</t>
+          <t>Share subscription receivable</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -13082,13 +12834,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F167" s="5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.044055</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -13119,12 +12871,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>Proceeds from shares issuance, net of issuance</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Share-based payments 10 - - 155,071 -</t>
+          <t>Proceeds from shares issuance, net of issuance total</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -13134,12 +12886,10 @@
         </is>
       </c>
       <c r="F168" s="5" t="n">
-        <v>0.155071</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.565011</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>3.401916</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -13170,27 +12920,29 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>Proceeds from shares issuance, net of issuance</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Foreign exchange movement - - - (88,909)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Effect of foreign exchange on cash</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F169" s="5" t="n">
+        <v>-0.020578</v>
+      </c>
+      <c r="G169" s="5" t="n">
         <v>-0.088909</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -13221,17 +12973,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>Proceeds from shares issuance, net of issuance</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
+          <t>Increase in cash</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -13240,10 +12992,10 @@
         </is>
       </c>
       <c r="F170" s="5" t="n">
-        <v>-0.918758</v>
+        <v>2.40363</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>-0.918758</v>
+        <v>0.306953</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -13274,25 +13026,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>Proceeds from shares issuance, net of issuance</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Balance at September 30, 2021 53,785,797 $ 10,438,790 $ 293,727 $ (109,487) $</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Cash, beginning of the period</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F171" s="5" t="n">
-        <v>8.587793</v>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>-2.035237</v>
+        <v>2.40363</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -13323,25 +13081,29 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Shares issued, re: Riverside’s warrants</t>
+          <t>Proceeds from shares issuance, net of issuance</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>For the year ended September 30, 2021 and the period form Incorporation on October 30, 2019 to September</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Cash, end of the period $</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F172" s="5" t="n">
-        <v>0.00202</v>
+        <v>2.40363</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>3e-05</v>
+        <v>2.710583</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -13367,33 +13129,27 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note      Shares       Amount       Reserves              e Loss               Deficit              Total</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Management and consulting fees 9 $</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance at Incorporation 1 $ 1 $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F173" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -13410,34 +13166,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J173" s="5" t="n">
-        <v>0.34693</v>
-      </c>
-      <c r="K173" s="5" t="n">
-        <v>0.8047260000000001</v>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note      Shares       Amount       Reserves              e Loss               Deficit              Total</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Adjustment for fractional shares (89) - - -</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -13458,30 +13214,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I174" s="5" t="n">
-        <v>0.001099</v>
-      </c>
-      <c r="J174" s="5" t="n">
-        <v>0.000745</v>
-      </c>
-      <c r="K174" s="5" t="n">
-        <v>0.000851</v>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note      Shares       Amount       Reserves              e Loss               Deficit              Total</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Director fees 9</t>
+          <t>Shares issued for mineral property 9 17,500,000 3,500,000 - -</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -13490,10 +13252,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F175" s="5" t="n">
+        <v>3.5</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -13515,112 +13275,128 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K175" s="5" t="n">
-        <v>0.0285</v>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Note      Shares       Amount       Reserves              e Loss               Deficit              Total</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E176" s="5" t="n">
-        <v>0.08106099999999999</v>
+          <t>Private placement 10 19,204,425 3,550,873 28,137 -</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F176" s="5" t="n">
-        <v>0.08106099999999999</v>
-      </c>
-      <c r="G176" s="5" t="n">
-        <v>0.03649</v>
-      </c>
-      <c r="H176" s="5" t="n">
-        <v>0.041222</v>
-      </c>
-      <c r="I176" s="5" t="n">
-        <v>0.08354</v>
-      </c>
-      <c r="J176" s="5" t="n">
-        <v>0.08708399999999999</v>
-      </c>
-      <c r="K176" s="5" t="n">
-        <v>0.061577</v>
+        <v>3.57901</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share issued, re: Riverside’s warrants exercised under Plan of Arrangement 10 155,923 30,055 - -</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F177" s="5" t="n">
-        <v>0.000266</v>
-      </c>
-      <c r="G177" s="5" t="n">
-        <v>-0.006268</v>
-      </c>
-      <c r="H177" s="5" t="n">
-        <v>-0.004305</v>
-      </c>
-      <c r="I177" s="5" t="n">
-        <v>0.018989</v>
-      </c>
-      <c r="J177" s="5" t="n">
-        <v>-0.004546</v>
-      </c>
-      <c r="K177" s="5" t="n">
-        <v>-0.102091</v>
+        <v>0.030055</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Investor relations and marketing</t>
+          <t>Share-based payments 10 - - 110,519 -</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13629,10 +13405,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F178" s="5" t="n">
+        <v>0.110519</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -13644,94 +13418,100 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I178" s="5" t="n">
-        <v>0.09033099999999999</v>
-      </c>
-      <c r="J178" s="5" t="n">
-        <v>0.151111</v>
-      </c>
-      <c r="K178" s="5" t="n">
-        <v>0.353768</v>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Share issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>General and administration</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="n">
-        <v>0.002273</v>
+          <t>Foreign exchange movement - - - (20,578)</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F179" s="5" t="n">
-        <v>0.002273</v>
-      </c>
-      <c r="G179" s="5" t="n">
-        <v>0.018128</v>
-      </c>
-      <c r="H179" s="5" t="n">
-        <v>0.031035</v>
-      </c>
-      <c r="I179" s="5" t="n">
-        <v>0.046445</v>
-      </c>
-      <c r="J179" s="5" t="n">
-        <v>0.043487</v>
-      </c>
-      <c r="K179" s="5" t="n">
-        <v>0.05447</v>
+        <v>-0.020578</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>on October 30, 2019 to September 30,</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Professional fees 9</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>on October 30, 2019 to September 30,</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F180" s="5" t="n">
+        <v>-1.116479</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>-1.116479</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -13743,27 +13523,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J180" s="5" t="n">
-        <v>0.136857</v>
-      </c>
-      <c r="K180" s="5" t="n">
-        <v>0.228079</v>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>on October 30, 2019 to September 30,</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Share-based compensation 8,9</t>
+          <t>Balance at September 30, 2020 36,860,260 7,080,929 138,656 (20,578)</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -13772,15 +13556,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F181" s="5" t="n">
+        <v>6.082528</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>-1.116479</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -13792,27 +13572,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J181" s="5" t="n">
-        <v>0.540527</v>
-      </c>
-      <c r="K181" s="5" t="n">
-        <v>0.151828</v>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>on October 30, 2019 to September 30,</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Travel and meals</t>
+          <t>Exercise of options 10 345,651 46,086 - -</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13821,59 +13605,59 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F182" s="5" t="n">
+        <v>0.046086</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H182" s="5" t="n">
-        <v>0.007749</v>
-      </c>
-      <c r="I182" s="5" t="n">
-        <v>0.005232</v>
-      </c>
-      <c r="J182" s="5" t="n">
-        <v>0.031365</v>
-      </c>
-      <c r="K182" s="5" t="n">
-        <v>0.050145</v>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Shares issued, re: Riverside’s warrants exercised under Plan of Arrangement 10 579,886 111,775 - -</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F183" s="5" t="n">
+        <v>0.111775</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -13885,289 +13669,319 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I183" s="5" t="n">
-        <v>-0.036561</v>
-      </c>
-      <c r="J183" s="5" t="n">
-        <v>-0.020004</v>
-      </c>
-      <c r="K183" s="5" t="n">
-        <v>-0.134141</v>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Private placement 10 16,000,000 3,200,000 - -</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G184" s="5" t="n">
-        <v>-0.918758</v>
-      </c>
-      <c r="H184" s="5" t="n">
-        <v>-0.66043</v>
-      </c>
-      <c r="I184" s="5" t="n">
-        <v>-0.746411</v>
-      </c>
-      <c r="J184" s="5" t="n">
-        <v>-1.313556</v>
-      </c>
-      <c r="K184" s="5" t="n">
-        <v>-1.497712</v>
+      <c r="F184" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Foreign exchange movements</t>
+          <t>Share-based payments 10 - - 155,071 -</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
-      <c r="E185" s="5" t="n">
-        <v>-0.020578</v>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F185" s="5" t="n">
-        <v>-0.020578</v>
-      </c>
-      <c r="G185" s="5" t="n">
-        <v>-0.088909</v>
-      </c>
-      <c r="H185" s="5" t="n">
-        <v>0.30945</v>
-      </c>
-      <c r="I185" s="5" t="n">
-        <v>0.7319830000000001</v>
-      </c>
-      <c r="J185" s="5" t="n">
-        <v>-1.043049</v>
-      </c>
-      <c r="K185" s="5" t="n">
-        <v>0.992096</v>
+        <v>0.155071</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Foreign exchange movement - - - (88,909)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G186" s="5" t="n">
-        <v>-1.007667</v>
-      </c>
-      <c r="H186" s="5" t="n">
-        <v>-0.35098</v>
-      </c>
-      <c r="I186" s="5" t="n">
-        <v>-0.014428</v>
-      </c>
-      <c r="J186" s="5" t="n">
-        <v>-2.356605</v>
-      </c>
-      <c r="K186" s="5" t="n">
-        <v>-0.505616</v>
+      <c r="F186" s="5" t="n">
+        <v>-0.088909</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Weighted average number of common</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>53.785797</v>
-      </c>
-      <c r="I187" s="5" t="n">
-        <v>69.23758599999999</v>
-      </c>
-      <c r="J187" s="5" t="n">
-        <v>76.43214399999999</v>
-      </c>
-      <c r="K187" s="5" t="n">
-        <v>96.12186</v>
+      <c r="F187" s="5" t="n">
+        <v>-0.918758</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>-0.918758</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Weighted average number of common</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Loss per share - basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Balance at September 30, 2021 53,785,797 $ 10,438,790 $ 293,727 $ (109,487) $</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F188" s="5" t="n">
+        <v>8.587793</v>
+      </c>
+      <c r="G188" s="5" t="n">
+        <v>-2.035237</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I188" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="J188" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="K188" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Shares issued, re: Riverside’s warrants</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Management and consulting fees 10 $</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E189" s="5" t="n">
-        <v>0.245397</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>For the year ended September 30, 2021 and the period form Incorporation on October 30, 2019 to September</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="G189" s="5" t="n">
+        <v>3e-05</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I189" s="5" t="n">
-        <v>0.424054</v>
-      </c>
-      <c r="J189" s="5" t="n">
-        <v>0.34693</v>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -14188,36 +14002,44 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Management and consulting fees 9 $</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E190" s="5" t="n">
-        <v>0.367357</v>
-      </c>
-      <c r="F190" s="5" t="n">
-        <v>0.367357</v>
-      </c>
-      <c r="G190" s="5" t="n">
-        <v>0.09918299999999999</v>
-      </c>
-      <c r="H190" s="5" t="n">
-        <v>0.091978</v>
-      </c>
-      <c r="I190" s="5" t="n">
-        <v>0.093113</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J190" s="5" t="n">
-        <v>0.136857</v>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.34693</v>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>0.8047260000000001</v>
       </c>
     </row>
     <row r="191">
@@ -14233,10 +14055,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Share-based compensation 9,10</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -14258,15 +14084,13 @@
         </is>
       </c>
       <c r="I191" s="5" t="n">
-        <v>0.020169</v>
+        <v>0.001099</v>
       </c>
       <c r="J191" s="5" t="n">
-        <v>0.540527</v>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000745</v>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>0.000851</v>
       </c>
     </row>
     <row r="192">
@@ -14282,7 +14106,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Management and consulting fees 11 $</t>
+          <t>Director fees 9</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -14295,27 +14119,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F192" s="5" t="n">
-        <v>0.245397</v>
-      </c>
-      <c r="G192" s="5" t="n">
-        <v>0.430598</v>
-      </c>
-      <c r="H192" s="5" t="n">
-        <v>0.248375</v>
-      </c>
-      <c r="I192" s="5" t="n">
-        <v>0.424054</v>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K192" s="5" t="n">
+        <v>0.0285</v>
       </c>
     </row>
     <row r="193">
@@ -14331,44 +14161,34 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Depreciation 8</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="n">
+        <v>0.08106099999999999</v>
+      </c>
+      <c r="F193" s="5" t="n">
+        <v>0.08106099999999999</v>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>0.03649</v>
       </c>
       <c r="H193" s="5" t="n">
-        <v>0.000511</v>
+        <v>0.041222</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>0.001099</v>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08354</v>
+      </c>
+      <c r="J193" s="5" t="n">
+        <v>0.08708399999999999</v>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>0.061577</v>
       </c>
     </row>
     <row r="194">
@@ -14384,38 +14204,36 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E194" s="5" t="n">
-        <v>0.179687</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F194" s="5" t="n">
-        <v>0.179687</v>
+        <v>0.000266</v>
       </c>
       <c r="G194" s="5" t="n">
-        <v>0.185556</v>
+        <v>-0.006268</v>
       </c>
       <c r="H194" s="5" t="n">
-        <v>0.177569</v>
+        <v>-0.004305</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>0.09033099999999999</v>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.018989</v>
+      </c>
+      <c r="J194" s="5" t="n">
+        <v>-0.004546</v>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>-0.102091</v>
       </c>
     </row>
     <row r="195">
@@ -14431,7 +14249,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Share-based compensation 10,11</t>
+          <t>Investor relations and marketing</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -14445,24 +14263,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G195" s="5" t="n">
-        <v>0.155071</v>
-      </c>
-      <c r="H195" s="5" t="n">
-        <v>0.06629599999999999</v>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I195" s="5" t="n">
-        <v>0.020169</v>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09033099999999999</v>
+      </c>
+      <c r="J195" s="5" t="n">
+        <v>0.151111</v>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>0.353768</v>
       </c>
     </row>
     <row r="196">
@@ -14473,49 +14291,39 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Weighted average number of common</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>General and administration</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="n">
+        <v>0.002273</v>
+      </c>
+      <c r="F196" s="5" t="n">
+        <v>0.002273</v>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>0.018128</v>
       </c>
       <c r="H196" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.031035</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.046445</v>
+      </c>
+      <c r="J196" s="5" t="n">
+        <v>0.043487</v>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>0.05447</v>
       </c>
     </row>
     <row r="197">
@@ -14531,12 +14339,12 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Professional fees 9</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -14549,26 +14357,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G197" s="5" t="n">
-        <v>-0.006268</v>
-      </c>
-      <c r="H197" s="5" t="n">
-        <v>-0.004305</v>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J197" s="5" t="n">
+        <v>0.136857</v>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>0.228079</v>
       </c>
     </row>
     <row r="198">
@@ -14579,12 +14387,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>common shares outstanding –</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>common shares outstanding – basic and diluted</t>
+          <t>Share-based compensation 8,9</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
@@ -14598,26 +14406,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G198" s="5" t="n">
-        <v>43.821961</v>
-      </c>
-      <c r="H198" s="5" t="n">
-        <v>53.785797</v>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J198" s="5" t="n">
+        <v>0.540527</v>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>0.151828</v>
       </c>
     </row>
     <row r="199">
@@ -14628,19 +14436,15 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>common shares outstanding –</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Travel and meals</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -14651,26 +14455,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G199" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007749</v>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>0.005232</v>
+      </c>
+      <c r="J199" s="5" t="n">
+        <v>0.031365</v>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>0.050145</v>
       </c>
     </row>
     <row r="200">
@@ -14681,17 +14481,23 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Incorporation on</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Notes September 30,</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" s="5" t="n">
-        <v>0.00202</v>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -14708,20 +14514,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I200" s="5" t="n">
+        <v>-0.036561</v>
+      </c>
+      <c r="J200" s="5" t="n">
+        <v>-0.020004</v>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>-0.134141</v>
       </c>
     </row>
     <row r="201">
@@ -14737,46 +14537,38 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E201" s="5" t="n">
-        <v>0.000266</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G201" s="5" t="n">
+        <v>-0.918758</v>
+      </c>
+      <c r="H201" s="5" t="n">
+        <v>-0.66043</v>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>-0.746411</v>
+      </c>
+      <c r="J201" s="5" t="n">
+        <v>-1.313556</v>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>-1.497712</v>
       </c>
     </row>
     <row r="202">
@@ -14792,40 +14584,30 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Property investigation and evaluation</t>
+          <t>Foreign exchange movements</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
       <c r="E202" s="5" t="n">
-        <v>0.127238</v>
+        <v>-0.020578</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>0.127238</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.020578</v>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>-0.088909</v>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>0.7319830000000001</v>
+      </c>
+      <c r="J202" s="5" t="n">
+        <v>-1.043049</v>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>0.992096</v>
       </c>
     </row>
     <row r="203">
@@ -14841,42 +14623,38 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Share-based compensation 9</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" s="5" t="n">
-        <v>0.110519</v>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G203" s="5" t="n">
+        <v>-1.007667</v>
+      </c>
+      <c r="H203" s="5" t="n">
+        <v>-0.35098</v>
+      </c>
+      <c r="I203" s="5" t="n">
+        <v>-0.014428</v>
+      </c>
+      <c r="J203" s="5" t="n">
+        <v>-2.356605</v>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>-0.505616</v>
       </c>
     </row>
     <row r="204">
@@ -14887,45 +14665,41 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Travel and entertainment</t>
+          <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
-      <c r="E204" s="5" t="n">
-        <v>0.002681</v>
-      </c>
-      <c r="F204" s="5" t="n">
-        <v>0.002681</v>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H204" s="5" t="n">
+        <v>53.785797</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>69.23758599999999</v>
+      </c>
+      <c r="J204" s="5" t="n">
+        <v>76.43214399999999</v>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>96.12186</v>
       </c>
     </row>
     <row r="205">
@@ -14936,47 +14710,47 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Net loss for the period</t>
+          <t>Loss per share - basic and diluted $</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E205" s="5" t="n">
-        <v>-1.116479</v>
-      </c>
-      <c r="F205" s="5" t="n">
-        <v>-1.116479</v>
-      </c>
-      <c r="G205" s="5" t="n">
-        <v>-0.918758</v>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I205" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J205" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>-2e-08</v>
       </c>
     </row>
     <row r="206">
@@ -14992,37 +14766,37 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the period $</t>
+          <t>Management and consulting fees 10 $</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
-        <v>-1.137057</v>
-      </c>
-      <c r="F206" s="5" t="n">
-        <v>-1.137057</v>
-      </c>
-      <c r="G206" s="5" t="n">
-        <v>-1.028245</v>
+        <v>0.245397</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I206" s="5" t="n">
+        <v>0.424054</v>
+      </c>
+      <c r="J206" s="5" t="n">
+        <v>0.34693</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -15043,37 +14817,31 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E207" s="5" t="n">
-        <v>4.570115</v>
+        <v>0.367357</v>
       </c>
       <c r="F207" s="5" t="n">
-        <v>4.570115</v>
+        <v>0.367357</v>
       </c>
       <c r="G207" s="5" t="n">
-        <v>43.821961</v>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09918299999999999</v>
+      </c>
+      <c r="H207" s="5" t="n">
+        <v>0.091978</v>
+      </c>
+      <c r="I207" s="5" t="n">
+        <v>0.093113</v>
+      </c>
+      <c r="J207" s="5" t="n">
+        <v>0.136857</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -15094,33 +14862,35 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Loss per share $</t>
+          <t>Share-based compensation 9,10</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
-      <c r="E208" s="5" t="n">
-        <v>-2.4e-07</v>
-      </c>
-      <c r="F208" s="5" t="n">
-        <v>-2.4e-07</v>
-      </c>
-      <c r="G208" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I208" s="5" t="n">
+        <v>0.020169</v>
+      </c>
+      <c r="J208" s="5" t="n">
+        <v>0.540527</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -15136,35 +14906,35 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Period from</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Notes 2021 September</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>Management and consulting fees 11 $</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F209" s="5" t="n">
-        <v>0.00202</v>
+        <v>0.245397</v>
       </c>
       <c r="G209" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.430598</v>
+      </c>
+      <c r="H209" s="5" t="n">
+        <v>0.248375</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>0.424054</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -15190,37 +14960,896 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
+          <t>Depreciation 8</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" s="5" t="n">
+        <v>0.000511</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>0.001099</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="n">
+        <v>0.179687</v>
+      </c>
+      <c r="F211" s="5" t="n">
+        <v>0.179687</v>
+      </c>
+      <c r="G211" s="5" t="n">
+        <v>0.185556</v>
+      </c>
+      <c r="H211" s="5" t="n">
+        <v>0.177569</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>0.09033099999999999</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Share-based compensation 10,11</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="n">
+        <v>0.155071</v>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>0.06629599999999999</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>0.020169</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Weighted average number of common</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I213" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="n">
+        <v>-0.006268</v>
+      </c>
+      <c r="H214" s="5" t="n">
+        <v>-0.004305</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>common shares outstanding –</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="n">
+        <v>43.821961</v>
+      </c>
+      <c r="H215" s="5" t="n">
+        <v>53.785797</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>common shares outstanding –</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H216" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Incorporation on</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Notes September 30,</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="n">
+        <v>0.000266</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Property investigation and evaluation</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" s="5" t="n">
+        <v>0.127238</v>
+      </c>
+      <c r="F219" s="5" t="n">
+        <v>0.127238</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Share-based compensation 9</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" s="5" t="n">
+        <v>0.110519</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Travel and entertainment</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" s="5" t="n">
+        <v>0.002681</v>
+      </c>
+      <c r="F221" s="5" t="n">
+        <v>0.002681</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Net loss for the period</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="n">
+        <v>-1.116479</v>
+      </c>
+      <c r="F222" s="5" t="n">
+        <v>-1.116479</v>
+      </c>
+      <c r="G222" s="5" t="n">
+        <v>-0.918758</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="n">
+        <v>-1.137057</v>
+      </c>
+      <c r="F223" s="5" t="n">
+        <v>-1.137057</v>
+      </c>
+      <c r="G223" s="5" t="n">
+        <v>-1.028245</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="n">
+        <v>4.570115</v>
+      </c>
+      <c r="F224" s="5" t="n">
+        <v>4.570115</v>
+      </c>
+      <c r="G224" s="5" t="n">
+        <v>43.821961</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Loss per share $</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" s="5" t="n">
+        <v>-2.4e-07</v>
+      </c>
+      <c r="F225" s="5" t="n">
+        <v>-2.4e-07</v>
+      </c>
+      <c r="G225" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Period from</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Notes 2021 September</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
           <t>Share-based compensation 10</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F210" s="5" t="n">
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="n">
         <v>0.110519</v>
       </c>
-      <c r="G210" s="5" t="n">
+      <c r="G227" s="5" t="n">
         <v>0.155071</v>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
         <is>
           <t>-</t>
         </is>
